--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.5735,0.0377,0.4122,0.0385</t>
-  </si>
-  <si>
-    <t>0.0406,0.0236,0.0012,0.9820</t>
-  </si>
-  <si>
-    <t>0.8427,0.0272,0.0341,0.0930</t>
-  </si>
-  <si>
-    <t>0.1922,0.0022,0.0062,0.9057</t>
-  </si>
-  <si>
-    <t>0.9963,0.0016,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9940,0.0028,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9958,0.0014,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9947,0.0032,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9825,0.0182,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.9708,0.0496,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.9955,0.0011,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.6648,0.0560,0.2958,0.0303</t>
-  </si>
-  <si>
-    <t>0.1465,0.0272,0.8366,0.0055</t>
-  </si>
-  <si>
-    <t>0.7068,0.0167,0.3724,0.0034</t>
-  </si>
-  <si>
-    <t>0.1526,0.0555,0.8086,0.0049</t>
-  </si>
-  <si>
-    <t>0.6950,0.0476,0.2545,0.0299</t>
-  </si>
-  <si>
-    <t>0.0283,0.9709,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.0061,0.9907,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.2260,0.8559,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.0644,0.9414,0.0099,0.0009</t>
-  </si>
-  <si>
-    <t>0.0160,0.9803,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.5662,0.0096,0.5130,0.0069</t>
-  </si>
-  <si>
-    <t>0.5165,0.0248,0.4761,0.0271</t>
-  </si>
-  <si>
-    <t>0.0047,0.0040,0.9932,0.0006</t>
-  </si>
-  <si>
-    <t>0.1130,0.0098,0.9084,0.0023</t>
-  </si>
-  <si>
-    <t>0.1346,0.0022,0.9312,0.0026</t>
-  </si>
-  <si>
-    <t>0.0623,0.0027,0.9566,0.0019</t>
-  </si>
-  <si>
-    <t>0.0053,0.0017,0.9894,0.0045</t>
-  </si>
-  <si>
-    <t>0.7197,0.2668,0.0621,0.0160</t>
-  </si>
-  <si>
-    <t>0.6451,0.1583,0.2688,0.0139</t>
-  </si>
-  <si>
-    <t>0.0006,0.0118,0.9970,0.0010</t>
-  </si>
-  <si>
-    <t>0.0508,0.8432,0.2870,0.0060</t>
-  </si>
-  <si>
-    <t>0.7796,0.1057,0.1283,0.0095</t>
-  </si>
-  <si>
-    <t>0.3387,0.0221,0.7017,0.0038</t>
-  </si>
-  <si>
-    <t>0.7111,0.3403,0.0226,0.0007</t>
-  </si>
-  <si>
-    <t>0.1220,0.8492,0.1508,0.0026</t>
-  </si>
-  <si>
-    <t>0.0101,0.9586,0.0741,0.0062</t>
-  </si>
-  <si>
-    <t>0.1594,0.2597,0.6999,0.0258</t>
-  </si>
-  <si>
-    <t>0.0087,0.2419,0.9291,0.0032</t>
-  </si>
-  <si>
-    <t>0.1163,0.0161,0.8890,0.0076</t>
-  </si>
-  <si>
-    <t>0.0281,0.0811,0.9414,0.0029</t>
-  </si>
-  <si>
-    <t>0.0244,0.9552,0.0512,0.0018</t>
-  </si>
-  <si>
-    <t>0.0944,0.0626,0.8596,0.0206</t>
-  </si>
-  <si>
-    <t>0.0784,0.7344,0.0600,0.7468</t>
-  </si>
-  <si>
-    <t>0.0043,0.9807,0.0089,0.0167</t>
-  </si>
-  <si>
-    <t>0.0036,0.9538,0.6317,0.0015</t>
-  </si>
-  <si>
-    <t>0.0019,0.9684,0.0545,0.0559</t>
-  </si>
-  <si>
-    <t>0.0184,0.3048,0.9231,0.0037</t>
-  </si>
-  <si>
-    <t>0.0011,0.1286,0.9847,0.0009</t>
-  </si>
-  <si>
-    <t>0.0261,0.0307,0.9448,0.0199</t>
-  </si>
-  <si>
-    <t>0.0113,0.0008,0.9925,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.0076,0.9957,0.0007</t>
-  </si>
-  <si>
-    <t>0.0128,0.3035,0.8980,0.0030</t>
-  </si>
-  <si>
-    <t>0.9112,0.1446,0.0034,0.0009</t>
-  </si>
-  <si>
-    <t>0.9683,0.0304,0.0054,0.0024</t>
-  </si>
-  <si>
-    <t>0.6508,0.0153,0.1829,0.0898</t>
-  </si>
-  <si>
-    <t>0.0020,0.0815,0.9932,0.0005</t>
-  </si>
-  <si>
-    <t>0.9765,0.0206,0.0041,0.0007</t>
-  </si>
-  <si>
-    <t>0.9891,0.0063,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9857,0.0078,0.0019,0.0020</t>
-  </si>
-  <si>
-    <t>0.0065,0.6798,0.9084,0.0018</t>
-  </si>
-  <si>
-    <t>0.0133,0.0836,0.9590,0.0071</t>
-  </si>
-  <si>
-    <t>0.0192,0.0816,0.9436,0.0084</t>
-  </si>
-  <si>
-    <t>0.0019,0.4629,0.9734,0.0014</t>
-  </si>
-  <si>
-    <t>0.0034,0.0091,0.9915,0.0016</t>
-  </si>
-  <si>
-    <t>0.0510,0.9304,0.0280,0.0011</t>
-  </si>
-  <si>
-    <t>0.0257,0.9829,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8510,0.0247,0.1181,0.0147</t>
-  </si>
-  <si>
-    <t>0.0415,0.8907,0.2298,0.0011</t>
-  </si>
-  <si>
-    <t>0.0104,0.0353,0.9803,0.0023</t>
-  </si>
-  <si>
-    <t>0.0031,0.8441,0.8230,0.0003</t>
-  </si>
-  <si>
-    <t>0.0035,0.6608,0.9346,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.9945,0.0482,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.9074,0.8718,0.0005</t>
-  </si>
-  <si>
-    <t>0.0071,0.0009,0.0950,0.9511</t>
-  </si>
-  <si>
-    <t>0.0024,0.0006,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.0030,0.0111,0.0002,0.9982</t>
-  </si>
-  <si>
-    <t>0.0057,0.0346,0.0032,0.9942</t>
-  </si>
-  <si>
-    <t>0.0128,0.0177,0.0054,0.9899</t>
-  </si>
-  <si>
-    <t>0.0078,0.0075,0.0061,0.9915</t>
-  </si>
-  <si>
-    <t>0.0014,0.9814,0.3679,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.6809,0.9252,0.0018</t>
-  </si>
-  <si>
-    <t>0.0096,0.7120,0.7819,0.0021</t>
-  </si>
-  <si>
-    <t>0.0170,0.1738,0.9227,0.0088</t>
-  </si>
-  <si>
-    <t>0.0006,0.9285,0.8278,0.0000</t>
-  </si>
-  <si>
-    <t>0.0094,0.6834,0.8272,0.0013</t>
-  </si>
-  <si>
-    <t>0.9886,0.0076,0.0026,0.0004</t>
-  </si>
-  <si>
-    <t>0.9782,0.0222,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.9527,0.0605,0.0075,0.0006</t>
-  </si>
-  <si>
-    <t>0.9778,0.0184,0.0023,0.0021</t>
-  </si>
-  <si>
-    <t>0.9772,0.0229,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.9915,0.0050,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9610,0.0307,0.0110,0.0022</t>
-  </si>
-  <si>
-    <t>0.9850,0.0159,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9925,0.0033,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9940,0.0021,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9901,0.0044,0.0004,0.0019</t>
-  </si>
-  <si>
-    <t>0.9925,0.0014,0.0002,0.0028</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9932,0.0030,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9957,0.0007,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9937,0.0029,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0024,0.9901,0.0234</t>
-  </si>
-  <si>
-    <t>0.0541,0.0148,0.9444,0.0019</t>
-  </si>
-  <si>
-    <t>0.6822,0.0061,0.3209,0.0148</t>
-  </si>
-  <si>
-    <t>0.2019,0.0065,0.8697,0.0022</t>
-  </si>
-  <si>
-    <t>0.1110,0.9210,0.0061,0.0004</t>
-  </si>
-  <si>
-    <t>0.1367,0.8684,0.0338,0.0010</t>
-  </si>
-  <si>
-    <t>0.1231,0.9004,0.0034,0.0010</t>
-  </si>
-  <si>
-    <t>0.6923,0.4056,0.0051,0.0042</t>
-  </si>
-  <si>
-    <t>0.0541,0.9528,0.0059,0.0005</t>
-  </si>
-  <si>
-    <t>0.0247,0.9705,0.0073,0.0003</t>
-  </si>
-  <si>
-    <t>0.7398,0.3538,0.0104,0.0007</t>
-  </si>
-  <si>
-    <t>0.6665,0.0112,0.0560,0.2331</t>
-  </si>
-  <si>
-    <t>0.5027,0.0335,0.5875,0.0117</t>
-  </si>
-  <si>
-    <t>0.4492,0.2304,0.4122,0.0094</t>
-  </si>
-  <si>
-    <t>0.3166,0.0337,0.6969,0.0196</t>
-  </si>
-  <si>
-    <t>0.0243,0.3040,0.0032,0.9652</t>
-  </si>
-  <si>
-    <t>0.0014,0.9949,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.0045,0.9843,0.0337,0.0025</t>
-  </si>
-  <si>
-    <t>0.0206,0.9507,0.0193,0.0217</t>
-  </si>
-  <si>
-    <t>0.0009,0.8606,0.9630,0.0005</t>
-  </si>
-  <si>
-    <t>0.0364,0.9629,0.0310,0.0002</t>
-  </si>
-  <si>
-    <t>0.7359,0.3431,0.0167,0.0013</t>
-  </si>
-  <si>
-    <t>0.4190,0.6666,0.0169,0.0004</t>
-  </si>
-  <si>
-    <t>0.9628,0.0278,0.0075,0.0017</t>
-  </si>
-  <si>
-    <t>0.9702,0.0061,0.0136,0.0049</t>
-  </si>
-  <si>
-    <t>0.9775,0.0082,0.0018,0.0055</t>
-  </si>
-  <si>
-    <t>0.9424,0.0175,0.0108,0.0204</t>
-  </si>
-  <si>
-    <t>0.9881,0.0038,0.0020,0.0031</t>
-  </si>
-  <si>
-    <t>0.9280,0.0485,0.0349,0.0043</t>
-  </si>
-  <si>
-    <t>0.9767,0.0194,0.0037,0.0026</t>
-  </si>
-  <si>
-    <t>0.9829,0.0090,0.0042,0.0012</t>
-  </si>
-  <si>
-    <t>0.0003,0.4557,0.9838,0.0000</t>
-  </si>
-  <si>
-    <t>0.0055,0.4123,0.9336,0.0003</t>
-  </si>
-  <si>
-    <t>0.0146,0.0678,0.9688,0.0014</t>
-  </si>
-  <si>
-    <t>0.0252,0.0390,0.9487,0.0006</t>
-  </si>
-  <si>
-    <t>0.7980,0.1339,0.0807,0.0105</t>
-  </si>
-  <si>
-    <t>0.7735,0.0057,0.3207,0.0029</t>
-  </si>
-  <si>
-    <t>0.2842,0.0029,0.8701,0.0010</t>
-  </si>
-  <si>
-    <t>0.4902,0.0487,0.5097,0.0229</t>
-  </si>
-  <si>
-    <t>0.0343,0.0172,0.0100,0.9751</t>
-  </si>
-  <si>
-    <t>0.0010,0.0012,0.0002,0.9993</t>
-  </si>
-  <si>
-    <t>0.0033,0.0207,0.0023,0.9961</t>
-  </si>
-  <si>
-    <t>0.0123,0.0011,0.0015,0.9938</t>
-  </si>
-  <si>
-    <t>0.0050,0.8313,0.6588,0.0004</t>
-  </si>
-  <si>
-    <t>0.9815,0.0084,0.0053,0.0010</t>
-  </si>
-  <si>
-    <t>0.5255,0.3510,0.1606,0.0127</t>
-  </si>
-  <si>
-    <t>0.9820,0.0119,0.0023,0.0015</t>
-  </si>
-  <si>
-    <t>0.8435,0.1442,0.0372,0.0036</t>
-  </si>
-  <si>
-    <t>0.9467,0.0128,0.0266,0.0067</t>
-  </si>
-  <si>
-    <t>0.2473,0.0558,0.0119,0.8448</t>
-  </si>
-  <si>
-    <t>0.9799,0.0054,0.0052,0.0038</t>
-  </si>
-  <si>
-    <t>0.0036,0.0597,0.9841,0.0091</t>
-  </si>
-  <si>
-    <t>0.8835,0.0034,0.0344,0.0502</t>
-  </si>
-  <si>
-    <t>0.9174,0.0159,0.0455,0.0174</t>
-  </si>
-  <si>
-    <t>0.6843,0.3223,0.0052,0.0080</t>
-  </si>
-  <si>
-    <t>0.9089,0.0261,0.0352,0.0113</t>
-  </si>
-  <si>
-    <t>0.8734,0.0544,0.0770,0.0093</t>
-  </si>
-  <si>
-    <t>0.3323,0.5185,0.2372,0.0261</t>
-  </si>
-  <si>
-    <t>0.7968,0.0409,0.1933,0.0114</t>
-  </si>
-  <si>
-    <t>0.8202,0.1164,0.0739,0.0092</t>
-  </si>
-  <si>
-    <t>0.9892,0.0068,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9766,0.0082,0.0028,0.0087</t>
-  </si>
-  <si>
-    <t>0.9884,0.0020,0.0007,0.0045</t>
-  </si>
-  <si>
-    <t>0.9848,0.0045,0.0023,0.0036</t>
-  </si>
-  <si>
-    <t>0.9850,0.0103,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.9670,0.0172,0.0116,0.0015</t>
-  </si>
-  <si>
-    <t>0.9812,0.0053,0.0023,0.0054</t>
-  </si>
-  <si>
-    <t>0.9850,0.0046,0.0028,0.0033</t>
-  </si>
-  <si>
-    <t>0.5920,0.4980,0.0122,0.0070</t>
-  </si>
-  <si>
-    <t>0.7386,0.3240,0.0147,0.0003</t>
-  </si>
-  <si>
-    <t>0.6946,0.3732,0.0237,0.0021</t>
-  </si>
-  <si>
-    <t>0.3848,0.5930,0.1842,0.0238</t>
-  </si>
-  <si>
-    <t>0.9643,0.0344,0.0059,0.0014</t>
-  </si>
-  <si>
-    <t>0.9237,0.0214,0.0077,0.0372</t>
-  </si>
-  <si>
-    <t>0.9735,0.0191,0.0040,0.0027</t>
-  </si>
-  <si>
-    <t>0.9559,0.0279,0.0085,0.0061</t>
-  </si>
-  <si>
-    <t>0.0074,0.1049,0.9770,0.0035</t>
-  </si>
-  <si>
-    <t>0.7732,0.1078,0.1295,0.0151</t>
-  </si>
-  <si>
-    <t>0.0071,0.0111,0.9899,0.0007</t>
-  </si>
-  <si>
-    <t>0.0066,0.0636,0.9798,0.0029</t>
-  </si>
-  <si>
-    <t>0.0766,0.0074,0.9368,0.0027</t>
-  </si>
-  <si>
-    <t>0.0024,0.1928,0.9824,0.0016</t>
-  </si>
-  <si>
-    <t>0.0065,0.0036,0.9921,0.0007</t>
-  </si>
-  <si>
-    <t>0.0046,0.0021,0.9924,0.0013</t>
-  </si>
-  <si>
-    <t>0.0008,0.0032,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.1058,0.0486,0.8430,0.0100</t>
-  </si>
-  <si>
-    <t>0.3940,0.0118,0.7113,0.0036</t>
-  </si>
-  <si>
-    <t>0.6404,0.0530,0.3432,0.0058</t>
-  </si>
-  <si>
-    <t>0.5083,0.1992,0.3397,0.0189</t>
-  </si>
-  <si>
-    <t>0.3180,0.2281,0.4429,0.0035</t>
-  </si>
-  <si>
-    <t>0.5889,0.0559,0.3874,0.0036</t>
-  </si>
-  <si>
-    <t>0.4363,0.0133,0.6338,0.0168</t>
-  </si>
-  <si>
-    <t>0.4427,0.0525,0.5388,0.0132</t>
-  </si>
-  <si>
-    <t>0.6696,0.5082,0.0077,0.0009</t>
-  </si>
-  <si>
-    <t>0.3056,0.8064,0.0072,0.0003</t>
-  </si>
-  <si>
-    <t>0.8909,0.1561,0.0076,0.0016</t>
-  </si>
-  <si>
-    <t>0.9345,0.0766,0.0087,0.0022</t>
-  </si>
-  <si>
-    <t>0.8179,0.2529,0.0108,0.0010</t>
-  </si>
-  <si>
-    <t>0.3813,0.1117,0.5617,0.0104</t>
-  </si>
-  <si>
-    <t>0.5728,0.0466,0.4303,0.0157</t>
-  </si>
-  <si>
-    <t>0.4378,0.1342,0.0605,0.3928</t>
-  </si>
-  <si>
-    <t>0.4043,0.0103,0.6622,0.0135</t>
-  </si>
-  <si>
-    <t>0.6334,0.0160,0.4311,0.0085</t>
-  </si>
-  <si>
-    <t>0.0105,0.0248,0.9521,0.0372</t>
-  </si>
-  <si>
-    <t>0.0160,0.2890,0.9015,0.0040</t>
-  </si>
-  <si>
-    <t>0.0357,0.0653,0.9258,0.0144</t>
-  </si>
-  <si>
-    <t>0.1323,0.0492,0.8714,0.0079</t>
-  </si>
-  <si>
-    <t>0.0014,0.9454,0.4792,0.0002</t>
-  </si>
-  <si>
-    <t>0.9771,0.0081,0.0017,0.0077</t>
-  </si>
-  <si>
-    <t>0.9922,0.0029,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9637,0.0445,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.9892,0.0071,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.9849,0.0185,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9850,0.0080,0.0023,0.0020</t>
-  </si>
-  <si>
-    <t>0.9911,0.0024,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.9913,0.0024,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.0419,0.0146,0.9316,0.0387</t>
-  </si>
-  <si>
-    <t>0.2199,0.5879,0.2724,0.0198</t>
-  </si>
-  <si>
-    <t>0.6776,0.0604,0.2405,0.0418</t>
-  </si>
-  <si>
-    <t>0.0055,0.0027,0.9919,0.0012</t>
-  </si>
-  <si>
-    <t>0.0039,0.0841,0.9759,0.0015</t>
-  </si>
-  <si>
-    <t>0.0326,0.0329,0.9531,0.0019</t>
-  </si>
-  <si>
-    <t>0.0004,0.0056,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.0515,0.0077,0.9477,0.0030</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0155,0.0018,0.9858,0.0017</t>
-  </si>
-  <si>
-    <t>0.1602,0.1001,0.7411,0.0101</t>
-  </si>
-  <si>
-    <t>0.5585,0.0211,0.4436,0.0245</t>
-  </si>
-  <si>
-    <t>0.4293,0.0546,0.5429,0.0390</t>
-  </si>
-  <si>
-    <t>0.7504,0.0151,0.1792,0.0341</t>
-  </si>
-  <si>
-    <t>0.9826,0.0091,0.0010,0.0017</t>
-  </si>
-  <si>
-    <t>0.9935,0.0028,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9927,0.0040,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9844,0.0123,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.9807,0.0079,0.0020,0.0037</t>
-  </si>
-  <si>
-    <t>0.9918,0.0035,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9949,0.0032,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9807,0.0118,0.0029,0.0022</t>
-  </si>
-  <si>
-    <t>0.0604,0.0078,0.9315,0.0091</t>
-  </si>
-  <si>
-    <t>0.0069,0.0105,0.9890,0.0012</t>
-  </si>
-  <si>
-    <t>0.0482,0.0641,0.9224,0.0077</t>
-  </si>
-  <si>
-    <t>0.0521,0.0363,0.9036,0.0012</t>
-  </si>
-  <si>
-    <t>0.0027,0.0088,0.9925,0.0020</t>
-  </si>
-  <si>
-    <t>0.4299,0.0126,0.4434,0.1106</t>
-  </si>
-  <si>
-    <t>0.0509,0.0125,0.9320,0.0131</t>
-  </si>
-  <si>
-    <t>0.0215,0.0172,0.9097,0.0938</t>
-  </si>
-  <si>
-    <t>0.7962,0.0012,0.0155,0.1482</t>
-  </si>
-  <si>
-    <t>0.0208,0.0814,0.0070,0.9792</t>
-  </si>
-  <si>
-    <t>0.0040,0.0123,0.0019,0.9967</t>
-  </si>
-  <si>
-    <t>0.0094,0.0004,0.0014,0.9936</t>
-  </si>
-  <si>
-    <t>0.0044,0.0011,0.0008,0.9973</t>
-  </si>
-  <si>
-    <t>0.6767,0.0868,0.0754,0.2748</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8511,0.0103,0.0925,0.0283</t>
+  </si>
+  <si>
+    <t>0.0150,0.0029,0.0005,0.9944</t>
+  </si>
+  <si>
+    <t>0.8939,0.0155,0.0346,0.0421</t>
+  </si>
+  <si>
+    <t>0.2898,0.0119,0.0036,0.8652</t>
+  </si>
+  <si>
+    <t>0.9944,0.0026,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0025,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9895,0.0024,0.0007,0.0042</t>
+  </si>
+  <si>
+    <t>0.9963,0.0010,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9723,0.0230,0.0063,0.0024</t>
+  </si>
+  <si>
+    <t>0.9888,0.0081,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.9955,0.0015,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9929,0.0007,0.0001,0.0028</t>
+  </si>
+  <si>
+    <t>0.6463,0.0742,0.3006,0.0364</t>
+  </si>
+  <si>
+    <t>0.1164,0.0161,0.8958,0.0020</t>
+  </si>
+  <si>
+    <t>0.3837,0.0186,0.6597,0.0044</t>
+  </si>
+  <si>
+    <t>0.0348,0.0091,0.9603,0.0012</t>
+  </si>
+  <si>
+    <t>0.6365,0.0704,0.3075,0.0102</t>
+  </si>
+  <si>
+    <t>0.0499,0.9586,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.0412,0.9720,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.7462,0.2428,0.0592,0.0092</t>
+  </si>
+  <si>
+    <t>0.0202,0.9779,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.0054,0.9927,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.4208,0.0313,0.6051,0.0229</t>
+  </si>
+  <si>
+    <t>0.2859,0.0119,0.7452,0.0120</t>
+  </si>
+  <si>
+    <t>0.0023,0.0008,0.9952,0.0018</t>
+  </si>
+  <si>
+    <t>0.1222,0.0078,0.9089,0.0068</t>
+  </si>
+  <si>
+    <t>0.0619,0.0049,0.9530,0.0045</t>
+  </si>
+  <si>
+    <t>0.0488,0.0059,0.9463,0.0138</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9926,0.0416</t>
+  </si>
+  <si>
+    <t>0.6346,0.3260,0.0930,0.0040</t>
+  </si>
+  <si>
+    <t>0.4513,0.2364,0.3789,0.0132</t>
+  </si>
+  <si>
+    <t>0.0075,0.0155,0.9762,0.0176</t>
+  </si>
+  <si>
+    <t>0.2035,0.7436,0.1440,0.0088</t>
+  </si>
+  <si>
+    <t>0.6883,0.3101,0.0456,0.0051</t>
+  </si>
+  <si>
+    <t>0.5252,0.0688,0.4193,0.0186</t>
+  </si>
+  <si>
+    <t>0.9102,0.1338,0.0068,0.0012</t>
+  </si>
+  <si>
+    <t>0.1396,0.7982,0.2502,0.0054</t>
+  </si>
+  <si>
+    <t>0.0608,0.3021,0.7480,0.0201</t>
+  </si>
+  <si>
+    <t>0.0389,0.1202,0.9120,0.0080</t>
+  </si>
+  <si>
+    <t>0.0579,0.3364,0.7842,0.0057</t>
+  </si>
+  <si>
+    <t>0.2644,0.0480,0.6686,0.0700</t>
+  </si>
+  <si>
+    <t>0.0208,0.1594,0.9184,0.0032</t>
+  </si>
+  <si>
+    <t>0.0040,0.9824,0.0360,0.0005</t>
+  </si>
+  <si>
+    <t>0.0122,0.0420,0.9660,0.0088</t>
+  </si>
+  <si>
+    <t>0.2653,0.5430,0.1068,0.4506</t>
+  </si>
+  <si>
+    <t>0.0164,0.9474,0.0444,0.0408</t>
+  </si>
+  <si>
+    <t>0.0066,0.9573,0.2804,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.9914,0.0482,0.0011</t>
+  </si>
+  <si>
+    <t>0.0133,0.2389,0.9464,0.0038</t>
+  </si>
+  <si>
+    <t>0.0004,0.0415,0.9960,0.0003</t>
+  </si>
+  <si>
+    <t>0.0442,0.0122,0.9493,0.0070</t>
+  </si>
+  <si>
+    <t>0.0602,0.0032,0.9626,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.0021,0.9944,0.0021</t>
+  </si>
+  <si>
+    <t>0.0032,0.0361,0.9889,0.0003</t>
+  </si>
+  <si>
+    <t>0.9600,0.0672,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.9608,0.0382,0.0096,0.0006</t>
+  </si>
+  <si>
+    <t>0.9216,0.0525,0.0286,0.0162</t>
+  </si>
+  <si>
+    <t>0.0045,0.1757,0.9813,0.0014</t>
+  </si>
+  <si>
+    <t>0.9815,0.0151,0.0029,0.0009</t>
+  </si>
+  <si>
+    <t>0.9723,0.0180,0.0087,0.0013</t>
+  </si>
+  <si>
+    <t>0.9336,0.1017,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9578,0.7641,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0598,0.9849,0.0022</t>
+  </si>
+  <si>
+    <t>0.0089,0.0125,0.9771,0.0091</t>
+  </si>
+  <si>
+    <t>0.0001,0.9194,0.9820,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0039,0.9964,0.0004</t>
+  </si>
+  <si>
+    <t>0.0555,0.9359,0.0195,0.0017</t>
+  </si>
+  <si>
+    <t>0.0126,0.9896,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.5598,0.0741,0.4587,0.0043</t>
+  </si>
+  <si>
+    <t>0.2912,0.2452,0.4903,0.0051</t>
+  </si>
+  <si>
+    <t>0.0735,0.1128,0.9060,0.0056</t>
+  </si>
+  <si>
+    <t>0.0014,0.5243,0.9686,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.9288,0.5264,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.9809,0.0999,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9907,0.1270,0.0003</t>
+  </si>
+  <si>
+    <t>0.0061,0.0025,0.1402,0.9441</t>
+  </si>
+  <si>
+    <t>0.0049,0.0198,0.0016,0.9960</t>
+  </si>
+  <si>
+    <t>0.0051,0.1128,0.0017,0.9930</t>
+  </si>
+  <si>
+    <t>0.0351,0.0273,0.0024,0.9825</t>
+  </si>
+  <si>
+    <t>0.0270,0.0027,0.0086,0.9815</t>
+  </si>
+  <si>
+    <t>0.0037,0.0036,0.0005,0.9979</t>
+  </si>
+  <si>
+    <t>0.0006,0.9744,0.6370,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.8903,0.9520,0.0003</t>
+  </si>
+  <si>
+    <t>0.0453,0.6516,0.6458,0.0117</t>
+  </si>
+  <si>
+    <t>0.0018,0.6735,0.8897,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9002,0.7174,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.8974,0.8782,0.0004</t>
+  </si>
+  <si>
+    <t>0.9940,0.0036,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9799,0.0279,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9739,0.0348,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9890,0.0047,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.9801,0.0117,0.0018,0.0039</t>
+  </si>
+  <si>
+    <t>0.9938,0.0044,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9863,0.0139,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9848,0.0114,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9932,0.0011,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9950,0.0021,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9943,0.0046,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9943,0.0016,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9880,0.0060,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9962,0.0003,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9922,0.0037,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9930,0.0025,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.0010,0.0013,0.9858,0.0277</t>
+  </si>
+  <si>
+    <t>0.0448,0.0103,0.9564,0.0007</t>
+  </si>
+  <si>
+    <t>0.7059,0.0283,0.2943,0.0265</t>
+  </si>
+  <si>
+    <t>0.1625,0.0100,0.8645,0.0037</t>
+  </si>
+  <si>
+    <t>0.0275,0.9701,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.0306,0.9710,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.0363,0.9654,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.1179,0.8935,0.0141,0.0013</t>
+  </si>
+  <si>
+    <t>0.0876,0.9363,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.0095,0.9821,0.0074,0.0010</t>
+  </si>
+  <si>
+    <t>0.7902,0.2966,0.0064,0.0006</t>
+  </si>
+  <si>
+    <t>0.6856,0.0873,0.2765,0.0268</t>
+  </si>
+  <si>
+    <t>0.5988,0.0191,0.4153,0.0283</t>
+  </si>
+  <si>
+    <t>0.8374,0.0239,0.1181,0.0056</t>
+  </si>
+  <si>
+    <t>0.3622,0.0601,0.6373,0.0115</t>
+  </si>
+  <si>
+    <t>0.0913,0.0142,0.0816,0.8968</t>
+  </si>
+  <si>
+    <t>0.0027,0.9897,0.0228,0.0013</t>
+  </si>
+  <si>
+    <t>0.0025,0.9804,0.0570,0.0193</t>
+  </si>
+  <si>
+    <t>0.0123,0.9534,0.0805,0.0230</t>
+  </si>
+  <si>
+    <t>0.0008,0.9771,0.7202,0.0002</t>
+  </si>
+  <si>
+    <t>0.0227,0.9734,0.0275,0.0002</t>
+  </si>
+  <si>
+    <t>0.6863,0.2947,0.0747,0.0033</t>
+  </si>
+  <si>
+    <t>0.7579,0.2886,0.0257,0.0015</t>
+  </si>
+  <si>
+    <t>0.9815,0.0096,0.0045,0.0010</t>
+  </si>
+  <si>
+    <t>0.9408,0.0223,0.0205,0.0169</t>
+  </si>
+  <si>
+    <t>0.9662,0.0053,0.0035,0.0161</t>
+  </si>
+  <si>
+    <t>0.9475,0.0230,0.0075,0.0168</t>
+  </si>
+  <si>
+    <t>0.9897,0.0033,0.0016,0.0029</t>
+  </si>
+  <si>
+    <t>0.8935,0.1021,0.0241,0.0090</t>
+  </si>
+  <si>
+    <t>0.9577,0.0303,0.0124,0.0030</t>
+  </si>
+  <si>
+    <t>0.9744,0.0157,0.0065,0.0024</t>
+  </si>
+  <si>
+    <t>0.0091,0.7597,0.6808,0.0021</t>
+  </si>
+  <si>
+    <t>0.0040,0.5257,0.9205,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.1288,0.9746,0.0005</t>
+  </si>
+  <si>
+    <t>0.0145,0.3110,0.8691,0.0014</t>
+  </si>
+  <si>
+    <t>0.7524,0.0353,0.1430,0.0616</t>
+  </si>
+  <si>
+    <t>0.4759,0.0170,0.6147,0.0113</t>
+  </si>
+  <si>
+    <t>0.2120,0.0202,0.8240,0.0125</t>
+  </si>
+  <si>
+    <t>0.7261,0.0980,0.1863,0.0078</t>
+  </si>
+  <si>
+    <t>0.0133,0.0022,0.0016,0.9924</t>
+  </si>
+  <si>
+    <t>0.0009,0.0013,0.0004,0.9992</t>
+  </si>
+  <si>
+    <t>0.0058,0.0350,0.0027,0.9937</t>
+  </si>
+  <si>
+    <t>0.1290,0.0019,0.0129,0.9022</t>
+  </si>
+  <si>
+    <t>0.0017,0.9537,0.5261,0.0003</t>
+  </si>
+  <si>
+    <t>0.9608,0.0144,0.0089,0.0147</t>
+  </si>
+  <si>
+    <t>0.2024,0.8334,0.0096,0.0034</t>
+  </si>
+  <si>
+    <t>0.9693,0.0071,0.0026,0.0140</t>
+  </si>
+  <si>
+    <t>0.6416,0.4508,0.0167,0.0012</t>
+  </si>
+  <si>
+    <t>0.9066,0.0158,0.0705,0.0103</t>
+  </si>
+  <si>
+    <t>0.1374,0.0354,0.0061,0.9393</t>
+  </si>
+  <si>
+    <t>0.9772,0.0125,0.0027,0.0022</t>
+  </si>
+  <si>
+    <t>0.0009,0.0115,0.9835,0.0357</t>
+  </si>
+  <si>
+    <t>0.9064,0.0158,0.0508,0.0191</t>
+  </si>
+  <si>
+    <t>0.8507,0.0138,0.0154,0.1215</t>
+  </si>
+  <si>
+    <t>0.5272,0.5640,0.0289,0.0022</t>
+  </si>
+  <si>
+    <t>0.8255,0.1792,0.0239,0.0016</t>
+  </si>
+  <si>
+    <t>0.8793,0.0702,0.0488,0.0062</t>
+  </si>
+  <si>
+    <t>0.6917,0.2191,0.0938,0.0260</t>
+  </si>
+  <si>
+    <t>0.6442,0.3109,0.0725,0.0047</t>
+  </si>
+  <si>
+    <t>0.7964,0.1844,0.0352,0.0213</t>
+  </si>
+  <si>
+    <t>0.9734,0.0116,0.0055,0.0050</t>
+  </si>
+  <si>
+    <t>0.9870,0.0056,0.0024,0.0023</t>
+  </si>
+  <si>
+    <t>0.9857,0.0045,0.0038,0.0016</t>
+  </si>
+  <si>
+    <t>0.9857,0.0046,0.0014,0.0043</t>
+  </si>
+  <si>
+    <t>0.9892,0.0046,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9681,0.0239,0.0074,0.0024</t>
+  </si>
+  <si>
+    <t>0.9736,0.0022,0.0009,0.0194</t>
+  </si>
+  <si>
+    <t>0.9878,0.0049,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.6009,0.5049,0.0208,0.0047</t>
+  </si>
+  <si>
+    <t>0.5773,0.5647,0.0082,0.0002</t>
+  </si>
+  <si>
+    <t>0.7949,0.2048,0.0394,0.0030</t>
+  </si>
+  <si>
+    <t>0.2296,0.6232,0.3555,0.0248</t>
+  </si>
+  <si>
+    <t>0.9237,0.1055,0.0073,0.0015</t>
+  </si>
+  <si>
+    <t>0.8639,0.0817,0.0368,0.0339</t>
+  </si>
+  <si>
+    <t>0.9663,0.0341,0.0050,0.0005</t>
+  </si>
+  <si>
+    <t>0.9347,0.0650,0.0144,0.0033</t>
+  </si>
+  <si>
+    <t>0.0018,0.0081,0.9951,0.0018</t>
+  </si>
+  <si>
+    <t>0.9228,0.1111,0.0068,0.0015</t>
+  </si>
+  <si>
+    <t>0.0008,0.0042,0.9964,0.0012</t>
+  </si>
+  <si>
+    <t>0.0328,0.2285,0.8937,0.0121</t>
+  </si>
+  <si>
+    <t>0.0798,0.0072,0.9436,0.0016</t>
+  </si>
+  <si>
+    <t>0.0398,0.3366,0.8070,0.0043</t>
+  </si>
+  <si>
+    <t>0.0299,0.0069,0.9715,0.0029</t>
+  </si>
+  <si>
+    <t>0.0036,0.0009,0.9961,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0034,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.4896,0.0311,0.5366,0.0133</t>
+  </si>
+  <si>
+    <t>0.1114,0.1559,0.7721,0.0190</t>
+  </si>
+  <si>
+    <t>0.5563,0.0257,0.4888,0.0162</t>
+  </si>
+  <si>
+    <t>0.2275,0.3499,0.4913,0.0099</t>
+  </si>
+  <si>
+    <t>0.0446,0.8769,0.1529,0.0012</t>
+  </si>
+  <si>
+    <t>0.3528,0.0620,0.6710,0.0084</t>
+  </si>
+  <si>
+    <t>0.5478,0.0394,0.4548,0.0124</t>
+  </si>
+  <si>
+    <t>0.6376,0.0390,0.3335,0.0022</t>
+  </si>
+  <si>
+    <t>0.9099,0.1161,0.0126,0.0009</t>
+  </si>
+  <si>
+    <t>0.9507,0.0717,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.6776,0.5124,0.0058,0.0003</t>
+  </si>
+  <si>
+    <t>0.9710,0.0263,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.8940,0.1190,0.0183,0.0024</t>
+  </si>
+  <si>
+    <t>0.2869,0.3742,0.3952,0.0194</t>
+  </si>
+  <si>
+    <t>0.6750,0.0120,0.4058,0.0029</t>
+  </si>
+  <si>
+    <t>0.8134,0.0113,0.1415,0.0206</t>
+  </si>
+  <si>
+    <t>0.6769,0.0149,0.3817,0.0036</t>
+  </si>
+  <si>
+    <t>0.7105,0.0043,0.3378,0.0139</t>
+  </si>
+  <si>
+    <t>0.1032,0.0076,0.8821,0.0385</t>
+  </si>
+  <si>
+    <t>0.0365,0.7243,0.6755,0.0239</t>
+  </si>
+  <si>
+    <t>0.0094,0.1014,0.9663,0.0006</t>
+  </si>
+  <si>
+    <t>0.0350,0.1030,0.9238,0.0022</t>
+  </si>
+  <si>
+    <t>0.0072,0.2782,0.9262,0.0007</t>
+  </si>
+  <si>
+    <t>0.9869,0.0049,0.0004,0.0031</t>
+  </si>
+  <si>
+    <t>0.9846,0.0108,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.9847,0.0076,0.0008,0.0035</t>
+  </si>
+  <si>
+    <t>0.9782,0.0126,0.0056,0.0029</t>
+  </si>
+  <si>
+    <t>0.9866,0.0156,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9382,0.0529,0.0148,0.0026</t>
+  </si>
+  <si>
+    <t>0.9842,0.0059,0.0009,0.0034</t>
+  </si>
+  <si>
+    <t>0.9850,0.0072,0.0015,0.0027</t>
+  </si>
+  <si>
+    <t>0.1754,0.0156,0.8622,0.0112</t>
+  </si>
+  <si>
+    <t>0.4294,0.4387,0.2198,0.0154</t>
+  </si>
+  <si>
+    <t>0.8327,0.0152,0.0929,0.0463</t>
+  </si>
+  <si>
+    <t>0.0188,0.0045,0.9784,0.0032</t>
+  </si>
+  <si>
+    <t>0.0016,0.0069,0.9943,0.0016</t>
+  </si>
+  <si>
+    <t>0.0457,0.1155,0.9072,0.0062</t>
+  </si>
+  <si>
+    <t>0.0004,0.0058,0.9980,0.0006</t>
+  </si>
+  <si>
+    <t>0.0998,0.0134,0.8968,0.0112</t>
+  </si>
+  <si>
+    <t>0.0003,0.0084,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.0061,0.0043,0.9915,0.0006</t>
+  </si>
+  <si>
+    <t>0.2344,0.1029,0.6634,0.0085</t>
+  </si>
+  <si>
+    <t>0.5645,0.0305,0.4073,0.0270</t>
+  </si>
+  <si>
+    <t>0.5659,0.0086,0.4750,0.0145</t>
+  </si>
+  <si>
+    <t>0.6496,0.0104,0.3040,0.0449</t>
+  </si>
+  <si>
+    <t>0.9698,0.0407,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9847,0.0152,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9909,0.0109,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9865,0.0088,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9877,0.0040,0.0009,0.0029</t>
+  </si>
+  <si>
+    <t>0.9849,0.0094,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0067,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9892,0.0040,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.0133,0.0169,0.9805,0.0011</t>
+  </si>
+  <si>
+    <t>0.0038,0.0087,0.9896,0.0025</t>
+  </si>
+  <si>
+    <t>0.0027,0.0175,0.9929,0.0004</t>
+  </si>
+  <si>
+    <t>0.0325,0.0425,0.9441,0.0013</t>
+  </si>
+  <si>
+    <t>0.0040,0.0069,0.9860,0.0092</t>
+  </si>
+  <si>
+    <t>0.2891,0.0209,0.4927,0.1946</t>
+  </si>
+  <si>
+    <t>0.1537,0.0138,0.8497,0.0180</t>
+  </si>
+  <si>
+    <t>0.0307,0.0934,0.8232,0.1545</t>
+  </si>
+  <si>
+    <t>0.8744,0.0010,0.0068,0.1033</t>
+  </si>
+  <si>
+    <t>0.0608,0.0033,0.0133,0.9534</t>
+  </si>
+  <si>
+    <t>0.0766,0.0060,0.0029,0.9661</t>
+  </si>
+  <si>
+    <t>0.0017,0.0006,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0084,0.0006,0.0008,0.9960</t>
+  </si>
+  <si>
+    <t>0.4721,0.0884,0.0107,0.5782</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2225,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2368,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,10 +2603,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,10 +2855,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2995,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3093,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3499,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3558,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3569,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4090,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4398,7 @@
         <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4622,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4717,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4731,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
